--- a/stories/arbres/ATOM-REL.AMI.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apolline est au parc. Papa est sur le banc. Apolline a des moules à gâteaux. Le sable est tiède. Fatou arrive près du bac. Apolline veut jouer. Papa dit : tu peux inviter. Inviter, c'est demander. Apolline dit : tu veux jouer avec nous ? Fatou secoue la tête. Fatou dit : non. Apolline a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Apolline dit : d'accord. Elle joue avec papa. Les moules se remplissent. Fatou joue avec un cerceau. Une abeille passe. Apolline n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Apolline sourit un peu. Le sable sent le soleil.</t>
+          <t>Apolline est au parc. Papa est sur le banc. Apolline a des moules à gâteaux. Le sable est tiède. Fatou arrive près du bac. Apolline veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Fatou secoue la tête. Non. Apolline a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les moules se remplissent. Fatou joue avec un cerceau. Une abeille passe. Apolline n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non. Apolline sourit un peu. Le sable sent le soleil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Apolline est au parc. Papa est sur le banc. Apolline a des moules à gâteaux. Le sable est tiède. Fatou arrive près du bac. Apolline veut jouer.
+papa|Tu peux inviter. Inviter, c'est demander.
+enfant-f|Tu veux jouer avec nous ?
+narrateur|Fatou secoue la tête.
+copine|Non.
+narrateur|Apolline a le ventre un peu serré. Papa s'approche.
+papa|On peut accepter un non. Accepter un non, c'est possible.
+enfant-f|D'accord. Elle joue avec papa.
+narrateur|Les moules se remplissent. Fatou joue avec un cerceau. Une abeille passe. Apolline n'insiste pas.
+papa|Merci. Tu as su inviter. Tu as su accepter un non.
+narrateur|Apolline sourit un peu. Le sable sent le soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Fatou dit non. Que fait Apolline ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Apolline a su inviter. Fatou a dit non. Apolline a pu accepter un non. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Apolline range un moule. Papa secoue le sable.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,11 @@
 narrateur|Apolline sourit un peu. Le sable sent le soleil.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|Fatou dit non. Que fait Apolline ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Apolline a su inviter. Fatou a dit non. Apolline a pu accepter un non. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Apolline range un moule. Papa secoue le sable.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apolline invite au bac à sable</t>
+          <t>Les gâteaux de sable de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah invite Aniss au bac à sable. Aniss dit non. Sarah accepte et fait des gâteaux avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apolline est au parc. Papa est sur le banc. Apolline a des moules à gâteaux. Le sable est tiède. Fatou arrive près du bac. Apolline veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Fatou secoue la tête. Non. Apolline a le ventre un peu serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les moules se remplissent. Fatou joue avec un cerceau. Une abeille passe. Apolline n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non. Apolline sourit un peu. Le sable sent le soleil.</t>
+          <t>Un seau jaune attend près du bac. Une feuille sèche colle au bord. Le sable sent le soleil. Une abeille passe, toute lente. Le banc du parc est chaud. Le sac de papa est dessous. Sarah, tu as vu le seau ? Il est jaune, papa. Oui. Il est à nous aujourd'hui. En ce moment, Sarah s'agenouille. Elle a des moules à gâteaux. Un moule est rose. Un moule est vert. Le sable est tiède sous les genoux. Je fais des gâteaux. Les gâteaux de sable, c'est bien. Aniss arrive près du bac. Il tient un cerceau rouge. Le cerceau tape contre sa jambe. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Aniss secoue la tête. Non. Sarah a le ventre un peu serré. Le moule rose reste dans sa main. Papa s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Sarah reste au bac. Elle joue avec papa. Les moules se remplissent. Le sable coule entre les doigts. Il est chaud et un peu rêche. Tu pousses bien le sable. Ça fait un gâteau. Oui. Un gâteau bien rond. Aniss joue avec le cerceau. Le cerceau roule sur l'herbe. Sarah accepte le non. Elle regarde ses gâteaux. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On continue nos gâteaux ? Oui, papa. Une abeille passe encore. Le sable sent toujours le soleil. Tu as fini ce gâteau-là ? Oui. Bravo. Tu as fait du bon travail. Sarah pose le moule rose. Le gâteau reste, tout croustillant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Apolline est au parc. Papa est sur le banc. Apolline a des moules à gâteaux. Le sable est tiède. Fatou arrive près du bac. Apolline veut jouer.
-papa|Tu peux inviter. Inviter, c'est demander.
+          <t>narrateur|Un seau jaune attend près du bac.
+narrateur|Une feuille sèche colle au bord.
+narrateur|Le sable sent le soleil.
+narrateur|Une abeille passe, toute lente.
+narrateur|Le banc du parc est chaud.
+narrateur|Le sac de papa est dessous.
+papa|Sarah, tu as vu le seau ?
+enfant-f|Il est jaune, papa.
+papa|Oui.
+papa|Il est à nous aujourd'hui.
+narrateur|En ce moment, Sarah s'agenouille.
+narrateur|Elle a des moules à gâteaux.
+narrateur|Un moule est rose.
+narrateur|Un moule est vert.
+narrateur|Le sable est tiède sous les genoux.
+enfant-f|Je fais des gâteaux.
+papa|Les gâteaux de sable, c'est bien.
+narrateur|Aniss arrive près du bac.
+narrateur|Il tient un cerceau rouge.
+narrateur|Le cerceau tape contre sa jambe.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
 enfant-f|Tu veux jouer avec nous ?
-narrateur|Fatou secoue la tête.
-copine|Non.
-narrateur|Apolline a le ventre un peu serré. Papa s'approche.
-papa|On peut accepter un non. Accepter un non, c'est possible.
-enfant-f|D'accord. Elle joue avec papa.
-narrateur|Les moules se remplissent. Fatou joue avec un cerceau. Une abeille passe. Apolline n'insiste pas.
-papa|Merci. Tu as su inviter. Tu as su accepter un non.
-narrateur|Apolline sourit un peu. Le sable sent le soleil.</t>
+narrateur|Aniss secoue la tête.
+copain|Non.
+narrateur|Sarah a le ventre un peu serré.
+narrateur|Le moule rose reste dans sa main.
+narrateur|Papa s'approche du bac.
+papa|On peut accepter un non.
+papa|Accepter un non, c'est possible.
+enfant-f|D'accord.
+narrateur|Sarah reste au bac.
+narrateur|Elle joue avec papa.
+narrateur|Les moules se remplissent.
+narrateur|Le sable coule entre les doigts.
+narrateur|Il est chaud et un peu rêche.
+papa|Tu pousses bien le sable.
+enfant-f|Ça fait un gâteau.
+papa|Oui.
+papa|Un gâteau bien rond.
+narrateur|Aniss joue avec le cerceau.
+narrateur|Le cerceau roule sur l'herbe.
+narrateur|Sarah accepte le non.
+narrateur|Elle regarde ses gâteaux.
+papa|Merci.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+enfant-f|Il a dit non.
+papa|Un non, c'est possible.
+papa|On continue nos gâteaux ?
+enfant-f|Oui, papa.
+narrateur|Une abeille passe encore.
+narrateur|Le sable sent toujours le soleil.
+papa|Tu as fini ce gâteau-là ?
+enfant-f|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Sarah pose le moule rose.
+narrateur|Le gâteau reste, tout croustillant.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1354,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fatou dit non. Que fait Apolline ?</t>
+          <t>Aniss dit non. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1510,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Fatou dit non. Que fait Apolline ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss dit non.
+narrateur|Que fait Sarah ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1538,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Apolline a su inviter. Fatou a dit non. Apolline a pu accepter un non. Papa est là.</t>
+          <t>Sarah a demandé. C'est inviter. Aniss a dit non. Sarah a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Sarah. J'ai dit d'accord. Oui. Un non, c'est possible. Le gâteau rose reste dans le bac. Le cerceau d'Aniss brille dans l'herbe. Tu as fini tes gâteaux de sable ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1682,10 +1742,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Apolline a su inviter. Fatou a dit non. Apolline a pu accepter un non. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a demandé.
+narrateur|C'est inviter.
+narrateur|Aniss a dit non.
+narrateur|Sarah a accepté le non.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+papa|Bravo, Sarah.
+enfant-f|J'ai dit d'accord.
+papa|Oui.
+papa|Un non, c'est possible.
+narrateur|Le gâteau rose reste dans le bac.
+narrateur|Le cerceau d'Aniss brille dans l'herbe.
+papa|Tu as fini tes gâteaux de sable ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Apolline range un moule. Papa secoue le sable.</t>
+          <t>Sarah range un moule. Le sable tombe sur ses chaussures. Je secoue le sable. Papa secoue le moule vert. Ça fait un petit nuage. Il vole. Oui. On le met dans le seau. Le seau jaune est un peu lourd. Tu prends ma main ? Oui. Ils laissent le bac. L'abeille n'est plus là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,10 +1918,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Apolline range un moule. Papa secoue le sable.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah range un moule.
+narrateur|Le sable tombe sur ses chaussures.
+papa|Je secoue le sable.
+narrateur|Papa secoue le moule vert.
+narrateur|Ça fait un petit nuage.
+enfant-f|Il vole.
+papa|Oui.
+papa|On le met dans le seau.
+narrateur|Le seau jaune est un peu lourd.
+papa|Tu prends ma main ?
+enfant-f|Oui.
+narrateur|Ils laissent le bac.
+narrateur|L'abeille n'est plus là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a invité. Elle a accepté un non. Les gâteaux de sable restent au soleil. Bravo, Sarah. On rentre ? Oui. On rentre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,10 +2097,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah a invité.
+narrateur|Elle a accepté un non.
+narrateur|Les gâteaux de sable restent au soleil.
+papa|Bravo, Sarah.
+enfant-f|On rentre ?
+papa|Oui.
+papa|On rentre.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un seau jaune attend près du bac. Une feuille sèche colle au bord. Le sable sent le soleil. Une abeille passe, toute lente. Le banc du parc est chaud. Le sac de papa est dessous. Sarah, tu as vu le seau ? Il est jaune, papa. Oui. Il est à nous aujourd'hui. En ce moment, Sarah s'agenouille. Elle a des moules à gâteaux. Un moule est rose. Un moule est vert. Le sable est tiède sous les genoux. Je fais des gâteaux. Les gâteaux de sable, c'est bien. Aniss arrive près du bac. Il tient un cerceau rouge. Le cerceau tape contre sa jambe. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Aniss secoue la tête. Non. Sarah a le ventre un peu serré. Le moule rose reste dans sa main. Papa s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Sarah reste au bac. Elle joue avec papa. Les moules se remplissent. Le sable coule entre les doigts. Il est chaud et un peu rêche. Tu pousses bien le sable. Ça fait un gâteau. Oui. Un gâteau bien rond. Aniss joue avec le cerceau. Le cerceau roule sur l'herbe. Sarah accepte le non. Elle regarde ses gâteaux. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On continue nos gâteaux ? Oui, papa. Une abeille passe encore. Le sable sent toujours le soleil. Tu as fini ce gâteau-là ? Oui. Bravo. Tu as fait du bon travail. Sarah pose le moule rose. Le gâteau reste, tout croustillant.</t>
+          <t>Un seau jaune attend près du bac. Une feuille sèche colle au bord. Le sable sent le soleil. Une abeille passe, toute lente. Le banc du parc est chaud. Le sac de papa est dessous. Sarah, tu as vu le seau ? Il est jaune, papa. Oui. Il est à nous aujourd'hui. En ce moment, Sarah s'agenouille. Elle a des moules à gâteaux. Un moule est rose. Un moule est vert. Le sable est tiède sous les genoux. Je fais des gâteaux. Les gâteaux de sable, c'est bien. Aniss arrive près du bac. Il tient un cerceau rouge. Le cerceau tape contre sa jambe. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Aniss secoue la tête. Non. Sarah a le ventre un peu serré. Le moule rose reste dans sa main. Papa s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Sarah reste au bac. Elle joue avec papa. Les moules se remplissent. Le sable coule entre les doigts. Il est chaud et un peu rêche. Tu pousses bien le sable. Ça fait un gâteau. Oui. Un gâteau bien rond. Aniss joue avec le cerceau. Le cerceau roule sur l'herbe. Sarah accepte le non. Elle regarde ses gâteaux. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On continue nos gâteaux ? Oui, papa. Une abeille passe encore. Le sable sent toujours le soleil. Tu as fini ce gâteau-là ? Oui. Bravo. Sarah pose le moule rose. Le gâteau reste, tout croustillant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Apolline est au parc. Papa est sur le banc. Apolline a des moules à gâteaux. Le sable est tiède. Fatou arrive près du bac. Apolline veut jouer. Papa dit : tu peux &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Inviter, c'est demander. Apolline dit : tu veux jouer avec nous ? Fatou secoue la tête. Fatou dit : non. Apolline a le ventre un peu serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Apolline dit : d'accord. Elle joue avec papa. Les moules se remplissent. Fatou joue avec un cerceau. Une abeille passe. Apolline n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Apolline sourit un peu. Le sable sent le soleil.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un seau jaune attend près du bac. Une feuille sèche colle au bord. Le sable sent le soleil. Une abeille passe, toute lente. Le banc du parc est chaud. Le sac de papa est dessous. Sarah, tu as vu le seau ? Il est jaune, papa. Oui. Il est à nous aujourd'hui. En ce moment, Sarah s'agenouille. Elle a des moules à gâteaux. Un moule est rose. Un moule est vert. Le sable est tiède sous les genoux. Je fais des gâteaux. Les gâteaux de sable, c'est bien. Aniss arrive près du bac. Il tient un cerceau rouge. Le cerceau tape contre sa jambe. Tu peux inviter. Inviter, c'est demander. Tu veux jouer avec nous ? Aniss secoue la tête. Non. Sarah a le ventre un peu serré. Le moule rose reste dans sa main. Papa s'approche du bac. On peut accepter un non. Accepter un non, c'est possible. D'accord. Sarah reste au bac. Elle joue avec papa. Les moules se remplissent. Le sable coule entre les doigts. Il est chaud et un peu rêche. Tu pousses bien le sable. Ça fait un gâteau. Oui. Un gâteau bien rond. Aniss joue avec le cerceau. Le cerceau roule sur l'herbe. Sarah accepte le non. Elle regarde ses gâteaux. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On continue nos gâteaux ? Oui, papa. Une abeille passe encore. Le sable sent toujours le soleil. Tu as fini ce gâteau-là ? Oui. Bravo. Sarah pose le moule rose. Le gâteau reste, tout croustillant.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 papa|Tu as fini ce gâteau-là ?
 enfant-f|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Sarah pose le moule rose.
 narrateur|Le gâteau reste, tout croustillant.</t>
         </is>
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Fatou dit non. Que fait Apolline ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss dit non. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1603,7 +1602,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Apolline a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Fatou a dit non. Apolline a pu accepter un non. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a demandé. C'est inviter. Aniss a dit non. Sarah a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Sarah. J'ai dit d'accord. Oui. Un non, c'est possible. Le gâteau rose reste dans le bac. Le cerceau d'Aniss brille dans l'herbe. Tu as fini tes gâteaux de sable ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1787,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Apolline range un moule. Papa secoue le sable.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range un moule. Le sable tombe sur ses chaussures. Je secoue le sable. Papa secoue le moule vert. Ça fait un petit nuage. Il vole. Oui. On le met dans le seau. Le seau jaune est un peu lourd. Tu prends ma main ? Oui. Ils laissent le bac. L'abeille n'est plus là.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1957,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah a invité. Elle a accepté un non. Les gâteaux de sable restent au soleil. Bravo, Sarah. On rentre ? Oui. On rentre. L'histoire est finie.</t>
+          <t>Sarah a invité. Elle a accepté un non. Les gâteaux de sable restent au soleil. Bravo, Sarah. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a invité. Elle a accepté un non. Les gâteaux de sable restent au soleil. Bravo, Sarah. On rentre ? Oui. On rentre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,8 +2102,7 @@
 papa|Bravo, Sarah.
 enfant-f|On rentre ?
 papa|Oui.
-papa|On rentre.
-narrateur|L'histoire est finie.</t>
+papa|On rentre.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apolline, Fatou, papa</t>
+          <t>Sarah, Aniss, papa</t>
         </is>
       </c>
     </row>
